--- a/data/nzd0406/nzd0406.xlsx
+++ b/data/nzd0406/nzd0406.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M435"/>
+  <dimension ref="A1:M437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20009,6 +20009,96 @@
         <v>325.56</v>
       </c>
       <c r="M435" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:07:11+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>312.98</v>
+      </c>
+      <c r="C436" t="n">
+        <v>303.59</v>
+      </c>
+      <c r="D436" t="n">
+        <v>311.51</v>
+      </c>
+      <c r="E436" t="n">
+        <v>323.63</v>
+      </c>
+      <c r="F436" t="n">
+        <v>328.98</v>
+      </c>
+      <c r="G436" t="n">
+        <v>332.58</v>
+      </c>
+      <c r="H436" t="n">
+        <v>332.01</v>
+      </c>
+      <c r="I436" t="n">
+        <v>325.4</v>
+      </c>
+      <c r="J436" t="n">
+        <v>321.49</v>
+      </c>
+      <c r="K436" t="n">
+        <v>319.03</v>
+      </c>
+      <c r="L436" t="n">
+        <v>325.28</v>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:23+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>312.98</v>
+      </c>
+      <c r="C437" t="n">
+        <v>303.22</v>
+      </c>
+      <c r="D437" t="n">
+        <v>311.65</v>
+      </c>
+      <c r="E437" t="n">
+        <v>323.86</v>
+      </c>
+      <c r="F437" t="n">
+        <v>328.61</v>
+      </c>
+      <c r="G437" t="n">
+        <v>332.62</v>
+      </c>
+      <c r="H437" t="n">
+        <v>332.4</v>
+      </c>
+      <c r="I437" t="n">
+        <v>325.1</v>
+      </c>
+      <c r="J437" t="n">
+        <v>320.75</v>
+      </c>
+      <c r="K437" t="n">
+        <v>318.04</v>
+      </c>
+      <c r="L437" t="n">
+        <v>324.76</v>
+      </c>
+      <c r="M437" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20025,7 +20115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B439"/>
+  <dimension ref="A1:B441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24418,6 +24508,26 @@
       </c>
       <c r="B439" t="n">
         <v>0.11</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>-0.59</v>
       </c>
     </row>
   </sheetData>
@@ -24586,28 +24696,28 @@
         <v>0.1019</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4987741478717231</v>
+        <v>-0.497845249386374</v>
       </c>
       <c r="J2" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K2" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1745591104178572</v>
+        <v>0.1753679543141662</v>
       </c>
       <c r="M2" t="n">
-        <v>6.799747687730711</v>
+        <v>6.772936696166613</v>
       </c>
       <c r="N2" t="n">
-        <v>67.11061195230181</v>
+        <v>66.80799712256903</v>
       </c>
       <c r="O2" t="n">
-        <v>8.192106685847165</v>
+        <v>8.173615914793711</v>
       </c>
       <c r="P2" t="n">
-        <v>325.3789899508306</v>
+        <v>325.3688632305108</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -24668,28 +24778,28 @@
         <v>0.1129</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4416398357250605</v>
+        <v>-0.444473085972345</v>
       </c>
       <c r="J3" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K3" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1902004331754417</v>
+        <v>0.1934817642534131</v>
       </c>
       <c r="M3" t="n">
-        <v>5.540336201368541</v>
+        <v>5.530505600408441</v>
       </c>
       <c r="N3" t="n">
-        <v>47.37425436012761</v>
+        <v>47.20574271294564</v>
       </c>
       <c r="O3" t="n">
-        <v>6.882895783035481</v>
+        <v>6.870643544308323</v>
       </c>
       <c r="P3" t="n">
-        <v>318.6161669533942</v>
+        <v>318.6470559674441</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -24750,28 +24860,28 @@
         <v>0.1421</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4877451688508728</v>
+        <v>-0.4873940128433427</v>
       </c>
       <c r="J4" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K4" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2976356972820374</v>
+        <v>0.2992992474619905</v>
       </c>
       <c r="M4" t="n">
-        <v>4.498526339157233</v>
+        <v>4.479712181160244</v>
       </c>
       <c r="N4" t="n">
-        <v>32.02603954527149</v>
+        <v>31.87990984834366</v>
       </c>
       <c r="O4" t="n">
-        <v>5.659155373840826</v>
+        <v>5.646229702052836</v>
       </c>
       <c r="P4" t="n">
-        <v>324.3441893649858</v>
+        <v>324.3403603762595</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -24832,28 +24942,28 @@
         <v>0.1919</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4660214014406466</v>
+        <v>-0.464848093776398</v>
       </c>
       <c r="J5" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K5" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4467310221974156</v>
+        <v>0.447674669817121</v>
       </c>
       <c r="M5" t="n">
-        <v>3.087457192259988</v>
+        <v>3.079976726893653</v>
       </c>
       <c r="N5" t="n">
-        <v>15.34411343622194</v>
+        <v>15.28214419588498</v>
       </c>
       <c r="O5" t="n">
-        <v>3.917156294586921</v>
+        <v>3.909238314030623</v>
       </c>
       <c r="P5" t="n">
-        <v>334.9760560773644</v>
+        <v>334.9632637984005</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -24914,28 +25024,28 @@
         <v>0.115</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4600242177100556</v>
+        <v>-0.4578940220492285</v>
       </c>
       <c r="J6" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K6" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5990502711029031</v>
+        <v>0.5982673595560073</v>
       </c>
       <c r="M6" t="n">
-        <v>2.188966408840743</v>
+        <v>2.188872890496306</v>
       </c>
       <c r="N6" t="n">
-        <v>8.013316807178395</v>
+        <v>8.003804596186241</v>
       </c>
       <c r="O6" t="n">
-        <v>2.830780247065885</v>
+        <v>2.829099608742372</v>
       </c>
       <c r="P6" t="n">
-        <v>338.7669444136015</v>
+        <v>338.7435891393313</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -24996,28 +25106,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.40779311331325</v>
+        <v>-0.4063987970736588</v>
       </c>
       <c r="J7" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K7" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5394412476989012</v>
+        <v>0.5397241615697533</v>
       </c>
       <c r="M7" t="n">
-        <v>2.077185658799702</v>
+        <v>2.073720588956234</v>
       </c>
       <c r="N7" t="n">
-        <v>8.032392651798576</v>
+        <v>8.007111289635198</v>
       </c>
       <c r="O7" t="n">
-        <v>2.834147605859401</v>
+        <v>2.82968395578644</v>
       </c>
       <c r="P7" t="n">
-        <v>342.0126638332739</v>
+        <v>341.9973753650821</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -25078,28 +25188,28 @@
         <v>0.0946</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3347923939322257</v>
+        <v>-0.336116659520931</v>
       </c>
       <c r="J8" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K8" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4637131599939192</v>
+        <v>0.4676634188492667</v>
       </c>
       <c r="M8" t="n">
-        <v>2.032611125186771</v>
+        <v>2.029973985668092</v>
       </c>
       <c r="N8" t="n">
-        <v>7.333700184811564</v>
+        <v>7.310678878628664</v>
       </c>
       <c r="O8" t="n">
-        <v>2.708080535141369</v>
+        <v>2.703826710169989</v>
       </c>
       <c r="P8" t="n">
-        <v>342.7725652768763</v>
+        <v>342.7870835357809</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -25160,28 +25270,28 @@
         <v>0.1082</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3012563330269162</v>
+        <v>-0.302120620414504</v>
       </c>
       <c r="J9" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K9" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3922540823651433</v>
+        <v>0.3957395397798235</v>
       </c>
       <c r="M9" t="n">
-        <v>2.165885887853489</v>
+        <v>2.160199260947791</v>
       </c>
       <c r="N9" t="n">
-        <v>7.955202074399177</v>
+        <v>7.923192147020123</v>
       </c>
       <c r="O9" t="n">
-        <v>2.820496777945186</v>
+        <v>2.814816538785454</v>
       </c>
       <c r="P9" t="n">
-        <v>334.3789703628408</v>
+        <v>334.3884483244906</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -25242,28 +25352,28 @@
         <v>0.0851</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2534604778525895</v>
+        <v>-0.2541259211675704</v>
       </c>
       <c r="J10" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K10" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2574987375141835</v>
+        <v>0.2602570695028485</v>
       </c>
       <c r="M10" t="n">
-        <v>2.495827147287826</v>
+        <v>2.488548005993337</v>
       </c>
       <c r="N10" t="n">
-        <v>10.48013453705476</v>
+        <v>10.43520390545077</v>
       </c>
       <c r="O10" t="n">
-        <v>3.237303590498544</v>
+        <v>3.230356622023452</v>
       </c>
       <c r="P10" t="n">
-        <v>328.7315237700993</v>
+        <v>328.7388235377279</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -25324,28 +25434,28 @@
         <v>0.0834</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2452009571728852</v>
+        <v>-0.2471158800905491</v>
       </c>
       <c r="J11" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K11" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2014750202816762</v>
+        <v>0.2052475151380557</v>
       </c>
       <c r="M11" t="n">
-        <v>2.897353871594926</v>
+        <v>2.893680206534188</v>
       </c>
       <c r="N11" t="n">
-        <v>13.48142771703919</v>
+        <v>13.44249909303788</v>
       </c>
       <c r="O11" t="n">
-        <v>3.671706376746266</v>
+        <v>3.666401381878133</v>
       </c>
       <c r="P11" t="n">
-        <v>327.3610726389474</v>
+        <v>327.3820737359894</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -25406,28 +25516,28 @@
         <v>0.0743</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2263377091897962</v>
+        <v>-0.2272553364497675</v>
       </c>
       <c r="J12" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K12" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2580735333583116</v>
+        <v>0.261321258071601</v>
       </c>
       <c r="M12" t="n">
-        <v>2.265252249037163</v>
+        <v>2.260258535277738</v>
       </c>
       <c r="N12" t="n">
-        <v>8.332119593001817</v>
+        <v>8.299152799538836</v>
       </c>
       <c r="O12" t="n">
-        <v>2.88654111230064</v>
+        <v>2.880825020638851</v>
       </c>
       <c r="P12" t="n">
-        <v>332.186426307172</v>
+        <v>332.1964901903822</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -25469,7 +25579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M435"/>
+  <dimension ref="A1:M437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54589,6 +54699,140 @@
         </is>
       </c>
     </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:07:11+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>-42.8275627891674,173.3350541742982</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>-42.82796905681832,173.3343374781741</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>-42.82848993403349,173.33376452808935</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>-42.82905609330018,173.33325704491665</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>-42.829592457526076,173.3327205915007</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>-42.830120521598815,173.3321779938731</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>-42.83063803553053,173.33159779060725</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>-42.831187899212146,173.33106960897817</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>-42.83174819220147,173.33059033924994</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>-42.83231337683399,173.33012773348145</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>-42.83291643300567,173.3297584486294</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:23+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>-42.8275627891674,173.3350541742982</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>-42.82796670845796,173.33433426686113</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>-42.82849080333623,173.33376576864734</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>-42.82905745998882,173.3332591593381</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>-42.82959031972336,173.33271711922953</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>-42.83012074931506,173.33217837307043</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>-42.83064001631976,173.33160173093273</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>-42.831186574474955,173.33106641002198</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>-42.83174497421476,173.33058241080684</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>-42.83230907166041,173.3301171264356</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>-42.83291417169182,173.32975287720544</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0406/nzd0406.xlsx
+++ b/data/nzd0406/nzd0406.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M437"/>
+  <dimension ref="A1:M440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20099,6 +20099,141 @@
         <v>324.76</v>
       </c>
       <c r="M437" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:07:16+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>312.68</v>
+      </c>
+      <c r="C438" t="n">
+        <v>303.53</v>
+      </c>
+      <c r="D438" t="n">
+        <v>311.52</v>
+      </c>
+      <c r="E438" t="n">
+        <v>324.19</v>
+      </c>
+      <c r="F438" t="n">
+        <v>328.29</v>
+      </c>
+      <c r="G438" t="n">
+        <v>332.9</v>
+      </c>
+      <c r="H438" t="n">
+        <v>333.31</v>
+      </c>
+      <c r="I438" t="n">
+        <v>325.03</v>
+      </c>
+      <c r="J438" t="n">
+        <v>320.98</v>
+      </c>
+      <c r="K438" t="n">
+        <v>317.99</v>
+      </c>
+      <c r="L438" t="n">
+        <v>325.14</v>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>311.81</v>
+      </c>
+      <c r="C439" t="n">
+        <v>303.75</v>
+      </c>
+      <c r="D439" t="n">
+        <v>311.59</v>
+      </c>
+      <c r="E439" t="n">
+        <v>324.2</v>
+      </c>
+      <c r="F439" t="n">
+        <v>328.66</v>
+      </c>
+      <c r="G439" t="n">
+        <v>333.12</v>
+      </c>
+      <c r="H439" t="n">
+        <v>333.77</v>
+      </c>
+      <c r="I439" t="n">
+        <v>325.03</v>
+      </c>
+      <c r="J439" t="n">
+        <v>321.26</v>
+      </c>
+      <c r="K439" t="n">
+        <v>317.74</v>
+      </c>
+      <c r="L439" t="n">
+        <v>325.15</v>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:31+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>311.39</v>
+      </c>
+      <c r="C440" t="n">
+        <v>303.7</v>
+      </c>
+      <c r="D440" t="n">
+        <v>311.81</v>
+      </c>
+      <c r="E440" t="n">
+        <v>324.1</v>
+      </c>
+      <c r="F440" t="n">
+        <v>328.79</v>
+      </c>
+      <c r="G440" t="n">
+        <v>333.72</v>
+      </c>
+      <c r="H440" t="n">
+        <v>334.57</v>
+      </c>
+      <c r="I440" t="n">
+        <v>324.95</v>
+      </c>
+      <c r="J440" t="n">
+        <v>321.13</v>
+      </c>
+      <c r="K440" t="n">
+        <v>317.72</v>
+      </c>
+      <c r="L440" t="n">
+        <v>324.53</v>
+      </c>
+      <c r="M440" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20115,7 +20250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B441"/>
+  <dimension ref="A1:B444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24528,6 +24663,36 @@
       </c>
       <c r="B441" t="n">
         <v>-0.59</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>-0.4</v>
       </c>
     </row>
   </sheetData>
@@ -24696,28 +24861,28 @@
         <v>0.1019</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.497845249386374</v>
+        <v>-0.4977515019266376</v>
       </c>
       <c r="J2" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K2" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1753679543141662</v>
+        <v>0.1773394829409833</v>
       </c>
       <c r="M2" t="n">
-        <v>6.772936696166613</v>
+        <v>6.729652300535458</v>
       </c>
       <c r="N2" t="n">
-        <v>66.80799712256903</v>
+        <v>66.35338142743926</v>
       </c>
       <c r="O2" t="n">
-        <v>8.173615914793711</v>
+        <v>8.145758493071057</v>
       </c>
       <c r="P2" t="n">
-        <v>325.3688632305108</v>
+        <v>325.3678462748592</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -24778,28 +24943,28 @@
         <v>0.1129</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.444473085972345</v>
+        <v>-0.4482416384944072</v>
       </c>
       <c r="J3" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K3" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1934817642534131</v>
+        <v>0.1981461348669564</v>
       </c>
       <c r="M3" t="n">
-        <v>5.530505600408441</v>
+        <v>5.513238713083889</v>
       </c>
       <c r="N3" t="n">
-        <v>47.20574271294564</v>
+        <v>46.94147164604655</v>
       </c>
       <c r="O3" t="n">
-        <v>6.870643544308323</v>
+        <v>6.851384651736213</v>
       </c>
       <c r="P3" t="n">
-        <v>318.6470559674441</v>
+        <v>318.6882731410918</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -24860,28 +25025,28 @@
         <v>0.1421</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4873940128433427</v>
+        <v>-0.4867601962636907</v>
       </c>
       <c r="J4" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K4" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2992992474619905</v>
+        <v>0.3016787558521475</v>
       </c>
       <c r="M4" t="n">
-        <v>4.479712181160244</v>
+        <v>4.452345338343393</v>
       </c>
       <c r="N4" t="n">
-        <v>31.87990984834366</v>
+        <v>31.66382132315851</v>
       </c>
       <c r="O4" t="n">
-        <v>5.646229702052836</v>
+        <v>5.627061517626985</v>
       </c>
       <c r="P4" t="n">
-        <v>324.3403603762595</v>
+        <v>324.3334257272339</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -24942,28 +25107,28 @@
         <v>0.1919</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.464848093776398</v>
+        <v>-0.4625681195011631</v>
       </c>
       <c r="J5" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K5" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L5" t="n">
-        <v>0.447674669817121</v>
+        <v>0.448352494019252</v>
       </c>
       <c r="M5" t="n">
-        <v>3.079976726893653</v>
+        <v>3.071813634355498</v>
       </c>
       <c r="N5" t="n">
-        <v>15.28214419588498</v>
+        <v>15.19903970544335</v>
       </c>
       <c r="O5" t="n">
-        <v>3.909238314030623</v>
+        <v>3.898594580800028</v>
       </c>
       <c r="P5" t="n">
-        <v>334.9632637984005</v>
+        <v>334.9383272282156</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -25024,28 +25189,28 @@
         <v>0.115</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4578940220492285</v>
+        <v>-0.4550197999274692</v>
       </c>
       <c r="J6" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K6" t="n">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5982673595560073</v>
+        <v>0.5975928616212978</v>
       </c>
       <c r="M6" t="n">
-        <v>2.188872890496306</v>
+        <v>2.18714208295689</v>
       </c>
       <c r="N6" t="n">
-        <v>8.003804596186241</v>
+        <v>7.98277906252409</v>
       </c>
       <c r="O6" t="n">
-        <v>2.829099608742372</v>
+        <v>2.825381224281794</v>
       </c>
       <c r="P6" t="n">
-        <v>338.7435891393313</v>
+        <v>338.7119683362745</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -25106,28 +25271,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4063987970736588</v>
+        <v>-0.4034996428277285</v>
       </c>
       <c r="J7" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K7" t="n">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5397241615697533</v>
+        <v>0.5385645707133219</v>
       </c>
       <c r="M7" t="n">
-        <v>2.073720588956234</v>
+        <v>2.072185064297599</v>
       </c>
       <c r="N7" t="n">
-        <v>8.007111289635198</v>
+        <v>7.98716599293241</v>
       </c>
       <c r="O7" t="n">
-        <v>2.82968395578644</v>
+        <v>2.826157460746377</v>
       </c>
       <c r="P7" t="n">
-        <v>341.9973753650821</v>
+        <v>341.9654776236455</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -25188,28 +25353,28 @@
         <v>0.0946</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.336116659520931</v>
+        <v>-0.3358577347719808</v>
       </c>
       <c r="J8" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K8" t="n">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4676634188492667</v>
+        <v>0.4706989483137353</v>
       </c>
       <c r="M8" t="n">
-        <v>2.029973985668092</v>
+        <v>2.019225162514971</v>
       </c>
       <c r="N8" t="n">
-        <v>7.310678878628664</v>
+        <v>7.262789920770856</v>
       </c>
       <c r="O8" t="n">
-        <v>2.703826710169989</v>
+        <v>2.694956385689916</v>
       </c>
       <c r="P8" t="n">
-        <v>342.7870835357809</v>
+        <v>342.7842260878602</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -25270,28 +25435,28 @@
         <v>0.1082</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.302120620414504</v>
+        <v>-0.3036700746073234</v>
       </c>
       <c r="J9" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K9" t="n">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3957395397798235</v>
+        <v>0.4012585944043338</v>
       </c>
       <c r="M9" t="n">
-        <v>2.160199260947791</v>
+        <v>2.153082732987039</v>
       </c>
       <c r="N9" t="n">
-        <v>7.923192147020123</v>
+        <v>7.878656779694317</v>
       </c>
       <c r="O9" t="n">
-        <v>2.814816538785454</v>
+        <v>2.806894508116455</v>
       </c>
       <c r="P9" t="n">
-        <v>334.3884483244906</v>
+        <v>334.4054932152285</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -25352,28 +25517,28 @@
         <v>0.0851</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2541259211675704</v>
+        <v>-0.2550696464695102</v>
       </c>
       <c r="J10" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K10" t="n">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2602570695028485</v>
+        <v>0.2643372615426518</v>
       </c>
       <c r="M10" t="n">
-        <v>2.488548005993337</v>
+        <v>2.477401441891053</v>
       </c>
       <c r="N10" t="n">
-        <v>10.43520390545077</v>
+        <v>10.36743157282298</v>
       </c>
       <c r="O10" t="n">
-        <v>3.230356622023452</v>
+        <v>3.219849619597626</v>
       </c>
       <c r="P10" t="n">
-        <v>328.7388235377279</v>
+        <v>328.7492039669014</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -25434,28 +25599,28 @@
         <v>0.0834</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2471158800905491</v>
+        <v>-0.2508143302636656</v>
       </c>
       <c r="J11" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K11" t="n">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2052475151380557</v>
+        <v>0.2117811522694806</v>
       </c>
       <c r="M11" t="n">
-        <v>2.893680206534188</v>
+        <v>2.892236283196516</v>
       </c>
       <c r="N11" t="n">
-        <v>13.44249909303788</v>
+        <v>13.40594536905022</v>
       </c>
       <c r="O11" t="n">
-        <v>3.666401381878133</v>
+        <v>3.661413029016287</v>
       </c>
       <c r="P11" t="n">
-        <v>327.3820737359894</v>
+        <v>327.4227593858944</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -25516,28 +25681,28 @@
         <v>0.0743</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2272553364497675</v>
+        <v>-0.2286736980257061</v>
       </c>
       <c r="J12" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K12" t="n">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="L12" t="n">
-        <v>0.261321258071601</v>
+        <v>0.266257804176717</v>
       </c>
       <c r="M12" t="n">
-        <v>2.260258535277738</v>
+        <v>2.253047499398097</v>
       </c>
       <c r="N12" t="n">
-        <v>8.299152799538836</v>
+        <v>8.251004488448162</v>
       </c>
       <c r="O12" t="n">
-        <v>2.880825020638851</v>
+        <v>2.872456176941288</v>
       </c>
       <c r="P12" t="n">
-        <v>332.1964901903822</v>
+        <v>332.2120972418568</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -25579,7 +25744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M437"/>
+  <dimension ref="A1:M440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54833,6 +54998,207 @@
         </is>
       </c>
     </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:07:16+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>-42.82756088510291,173.33505157053247</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>-42.827968676003124,173.33433695742062</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>-42.82848999612655,173.33376461670065</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>-42.82905942088982,173.33326219307338</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>-42.8295884708128,173.33271411618438</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>-42.83012234332878,173.3321810274519</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>-42.83064463816076,173.33161092502652</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>-42.8311862653696,173.33106566359888</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>-42.831745974399865,173.33058487505258</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>-42.832308854227385,173.33011659072625</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>-42.83291582419044,173.3297569486306</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>-42.82755536331556,173.33504401961287</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>-42.82797007232547,173.33433886685006</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>-42.82849043077793,173.33376523697962</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>-42.82905948031107,173.33326228500476</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>-42.829590608615625,173.33271758845535</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>-42.83012359576809,173.3321831130374</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>-42.830646974475705,173.33161557259095</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>-42.8311862653696,173.33106566359888</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>-42.83174719201645,173.33058787500403</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>-42.832307767062154,173.33011391217954</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>-42.83291586767724,173.32975705577334</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:31+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>-42.82755269762493,173.33504037434182</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>-42.82796975497948,173.3343384328888</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>-42.82849179682506,173.3337671864279</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>-42.82905888609864,173.33326136569102</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>-42.82959135973551,173.33271880844248</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>-42.830127011511486,173.3321888009983</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>-42.830651037631675,173.33162365531248</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>-42.83118591210633,173.33106481054392</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>-42.83174662669449,173.3305864821694</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>-42.832307680088945,173.3301136978958</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>-42.83291317149519,173.3297504129219</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0406/nzd0406.xlsx
+++ b/data/nzd0406/nzd0406.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M440"/>
+  <dimension ref="A1:M441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20234,6 +20234,51 @@
         <v>324.53</v>
       </c>
       <c r="M440" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>312.03</v>
+      </c>
+      <c r="C441" t="n">
+        <v>304.53</v>
+      </c>
+      <c r="D441" t="n">
+        <v>312.32</v>
+      </c>
+      <c r="E441" t="n">
+        <v>323.74</v>
+      </c>
+      <c r="F441" t="n">
+        <v>328.25</v>
+      </c>
+      <c r="G441" t="n">
+        <v>334.26</v>
+      </c>
+      <c r="H441" t="n">
+        <v>335.71</v>
+      </c>
+      <c r="I441" t="n">
+        <v>324.74</v>
+      </c>
+      <c r="J441" t="n">
+        <v>320.61</v>
+      </c>
+      <c r="K441" t="n">
+        <v>317.18</v>
+      </c>
+      <c r="L441" t="n">
+        <v>324.25</v>
+      </c>
+      <c r="M441" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20250,7 +20295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B444"/>
+  <dimension ref="A1:B445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24693,6 +24738,16 @@
       </c>
       <c r="B444" t="n">
         <v>-0.4</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>0.21</v>
       </c>
     </row>
   </sheetData>
@@ -24861,28 +24916,28 @@
         <v>0.1019</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4977515019266376</v>
+        <v>-0.4976725280399771</v>
       </c>
       <c r="J2" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K2" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1773394829409833</v>
+        <v>0.177971237871154</v>
       </c>
       <c r="M2" t="n">
-        <v>6.729652300535458</v>
+        <v>6.714732560345533</v>
       </c>
       <c r="N2" t="n">
-        <v>66.35338142743926</v>
+        <v>66.20265584583342</v>
       </c>
       <c r="O2" t="n">
-        <v>8.145758493071057</v>
+        <v>8.136501449998851</v>
       </c>
       <c r="P2" t="n">
-        <v>325.3678462748592</v>
+        <v>325.3669793828483</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -24943,28 +24998,28 @@
         <v>0.1129</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4482416384944072</v>
+        <v>-0.449085030719804</v>
       </c>
       <c r="J3" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K3" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1981461348669564</v>
+        <v>0.1994543764804317</v>
       </c>
       <c r="M3" t="n">
-        <v>5.513238713083889</v>
+        <v>5.505279092616942</v>
       </c>
       <c r="N3" t="n">
-        <v>46.94147164604655</v>
+        <v>46.84363190964451</v>
       </c>
       <c r="O3" t="n">
-        <v>6.851384651736213</v>
+        <v>6.844240784020132</v>
       </c>
       <c r="P3" t="n">
-        <v>318.6882731410918</v>
+        <v>318.6975310111688</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -25025,28 +25080,28 @@
         <v>0.1421</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4867601962636907</v>
+        <v>-0.4862460922435516</v>
       </c>
       <c r="J4" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K4" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3016787558521475</v>
+        <v>0.3021899428954132</v>
       </c>
       <c r="M4" t="n">
-        <v>4.452345338343393</v>
+        <v>4.444867375033869</v>
       </c>
       <c r="N4" t="n">
-        <v>31.66382132315851</v>
+        <v>31.59514480440625</v>
       </c>
       <c r="O4" t="n">
-        <v>5.627061517626985</v>
+        <v>5.620955862164926</v>
       </c>
       <c r="P4" t="n">
-        <v>324.3334257272339</v>
+        <v>324.3277824356772</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -25107,28 +25162,28 @@
         <v>0.1919</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4625681195011631</v>
+        <v>-0.4619860239620704</v>
       </c>
       <c r="J5" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K5" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L5" t="n">
-        <v>0.448352494019252</v>
+        <v>0.448809268559701</v>
       </c>
       <c r="M5" t="n">
-        <v>3.071813634355498</v>
+        <v>3.06811007488712</v>
       </c>
       <c r="N5" t="n">
-        <v>15.19903970544335</v>
+        <v>15.16870998317663</v>
       </c>
       <c r="O5" t="n">
-        <v>3.898594580800028</v>
+        <v>3.894702810636087</v>
       </c>
       <c r="P5" t="n">
-        <v>334.9383272282156</v>
+        <v>334.9319375974944</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -25189,28 +25244,28 @@
         <v>0.115</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4550197999274692</v>
+        <v>-0.4542062341666243</v>
       </c>
       <c r="J6" t="n">
+        <v>440</v>
+      </c>
+      <c r="K6" t="n">
         <v>439</v>
       </c>
-      <c r="K6" t="n">
-        <v>438</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.5975928616212978</v>
+        <v>0.5976073251954819</v>
       </c>
       <c r="M6" t="n">
-        <v>2.18714208295689</v>
+        <v>2.185902581709275</v>
       </c>
       <c r="N6" t="n">
-        <v>7.98277906252409</v>
+        <v>7.972728204980498</v>
       </c>
       <c r="O6" t="n">
-        <v>2.825381224281794</v>
+        <v>2.823601991248146</v>
       </c>
       <c r="P6" t="n">
-        <v>338.7119683362745</v>
+        <v>338.7029867631741</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -25271,28 +25326,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4034996428277285</v>
+        <v>-0.4021020857800998</v>
       </c>
       <c r="J7" t="n">
+        <v>440</v>
+      </c>
+      <c r="K7" t="n">
         <v>439</v>
       </c>
-      <c r="K7" t="n">
-        <v>438</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.5385645707133219</v>
+        <v>0.5372505629552209</v>
       </c>
       <c r="M7" t="n">
-        <v>2.072185064297599</v>
+        <v>2.073669623502891</v>
       </c>
       <c r="N7" t="n">
-        <v>7.98716599293241</v>
+        <v>7.992972063326666</v>
       </c>
       <c r="O7" t="n">
-        <v>2.826157460746377</v>
+        <v>2.827184476352165</v>
       </c>
       <c r="P7" t="n">
-        <v>341.9654776236455</v>
+        <v>341.9500489252055</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -25353,28 +25408,28 @@
         <v>0.0946</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3358577347719808</v>
+        <v>-0.3349772442112215</v>
       </c>
       <c r="J8" t="n">
+        <v>440</v>
+      </c>
+      <c r="K8" t="n">
         <v>439</v>
       </c>
-      <c r="K8" t="n">
-        <v>438</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.4706989483137353</v>
+        <v>0.4702246197275898</v>
       </c>
       <c r="M8" t="n">
-        <v>2.019225162514971</v>
+        <v>2.019424469373587</v>
       </c>
       <c r="N8" t="n">
-        <v>7.262789920770856</v>
+        <v>7.255772249049267</v>
       </c>
       <c r="O8" t="n">
-        <v>2.694956385689916</v>
+        <v>2.693654070041152</v>
       </c>
       <c r="P8" t="n">
-        <v>342.7842260878602</v>
+        <v>342.7745056808369</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -25435,28 +25490,28 @@
         <v>0.1082</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3036700746073234</v>
+        <v>-0.3042804582223873</v>
       </c>
       <c r="J9" t="n">
+        <v>440</v>
+      </c>
+      <c r="K9" t="n">
         <v>439</v>
       </c>
-      <c r="K9" t="n">
-        <v>438</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.4012585944043338</v>
+        <v>0.4032046589915216</v>
       </c>
       <c r="M9" t="n">
-        <v>2.153082732987039</v>
+        <v>2.15120600998521</v>
       </c>
       <c r="N9" t="n">
-        <v>7.878656779694317</v>
+        <v>7.865287988859524</v>
       </c>
       <c r="O9" t="n">
-        <v>2.806894508116455</v>
+        <v>2.804512076789744</v>
       </c>
       <c r="P9" t="n">
-        <v>334.4054932152285</v>
+        <v>334.4122317056147</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -25517,28 +25572,28 @@
         <v>0.0851</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2550696464695102</v>
+        <v>-0.2555905121097631</v>
       </c>
       <c r="J10" t="n">
+        <v>440</v>
+      </c>
+      <c r="K10" t="n">
         <v>439</v>
       </c>
-      <c r="K10" t="n">
-        <v>438</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.2643372615426518</v>
+        <v>0.2659774278209776</v>
       </c>
       <c r="M10" t="n">
-        <v>2.477401441891053</v>
+        <v>2.47501176154996</v>
       </c>
       <c r="N10" t="n">
-        <v>10.36743157282298</v>
+        <v>10.34714924275245</v>
       </c>
       <c r="O10" t="n">
-        <v>3.219849619597626</v>
+        <v>3.216698500443032</v>
       </c>
       <c r="P10" t="n">
-        <v>328.7492039669014</v>
+        <v>328.7549542000708</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -25599,28 +25654,28 @@
         <v>0.0834</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2508143302636656</v>
+        <v>-0.2522853674185631</v>
       </c>
       <c r="J11" t="n">
+        <v>440</v>
+      </c>
+      <c r="K11" t="n">
         <v>439</v>
       </c>
-      <c r="K11" t="n">
-        <v>438</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.2117811522694806</v>
+        <v>0.2141898285235125</v>
       </c>
       <c r="M11" t="n">
-        <v>2.892236283196516</v>
+        <v>2.892902956788869</v>
       </c>
       <c r="N11" t="n">
-        <v>13.40594536905022</v>
+        <v>13.40199805335566</v>
       </c>
       <c r="O11" t="n">
-        <v>3.661413029016287</v>
+        <v>3.660873946662964</v>
       </c>
       <c r="P11" t="n">
-        <v>327.4227593858944</v>
+        <v>327.4389992872964</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -25681,28 +25736,28 @@
         <v>0.0743</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2286736980257061</v>
+        <v>-0.2294245203594275</v>
       </c>
       <c r="J12" t="n">
+        <v>440</v>
+      </c>
+      <c r="K12" t="n">
         <v>439</v>
       </c>
-      <c r="K12" t="n">
-        <v>438</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.266257804176717</v>
+        <v>0.2682895902919528</v>
       </c>
       <c r="M12" t="n">
-        <v>2.253047499398097</v>
+        <v>2.252255842956488</v>
       </c>
       <c r="N12" t="n">
-        <v>8.251004488448162</v>
+        <v>8.239136531138167</v>
       </c>
       <c r="O12" t="n">
-        <v>2.872456176941288</v>
+        <v>2.870389613125397</v>
       </c>
       <c r="P12" t="n">
-        <v>332.2120972418568</v>
+        <v>332.2203861423984</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -25744,7 +25799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M440"/>
+  <dimension ref="A1:M441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55199,6 +55254,73 @@
         </is>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>-42.82755675962965,173.3350459290407</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>-42.82797502292259,173.33434563664596</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>-42.82849496357058,173.33377170560374</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>-42.82905674693388,173.3332580561617</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>-42.829588239698985,173.33271374080374</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>-42.830130085680274,173.33219392016366</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>-42.83065682762796,173.3316351731925</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>-42.83118498479022,173.3310625712747</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>-42.8317443654064,173.3305809108312</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>-42.83230533181186,173.33010791223532</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>-42.83291195386448,173.32974741292466</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
